--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,113 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129499211</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96201</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holmtorp, SO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595705</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6549846</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe på nyligen avverkat hygge där granbarkborredödade granar avverkats och levande tallar, lövträd och enstaka granar sparats.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96263</v>
+        <v>96267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129499211</v>
       </c>
       <c r="B3" t="n">
-        <v>96269</v>
+        <v>96279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131582075</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57889</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fredsbacken, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6549756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande på torra alar utmed stranden. Spillkråka är regelbundet förekommande inom området.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116148246</v>
+        <v>79281229</v>
       </c>
       <c r="B2" t="n">
-        <v>90415</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp, SO om, Srm</t>
+          <t>Fredsbacken, NV om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595681</v>
+        <v>595776</v>
       </c>
       <c r="R2" t="n">
-        <v>6549823</v>
+        <v>6549798</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,17 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På grov granlåga i blockrik sluttning i gränsen mot granbestånd där de flesta granarna dödats av granbarkborrar.</t>
+          <t>På granlåga nära fastighetsgräns, strax öster om en ek.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,52 +781,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129499211</v>
+        <v>96870887</v>
       </c>
       <c r="B3" t="n">
-        <v>96279</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmtorp, SO om, Srm</t>
+          <t>Fredsbacken, NV om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595705</v>
+        <v>595772</v>
       </c>
       <c r="R3" t="n">
-        <v>6549846</v>
+        <v>6549794</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe på nyligen avverkat hygge där granbarkborredödade granar avverkats och levande tallar, lövträd och enstaka granar sparats.</t>
+          <t>Återfynd. På grövsta granlågan ca 1m från roten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131582075</v>
+        <v>116148246</v>
       </c>
       <c r="B4" t="n">
-        <v>57911</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,49 +898,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fredsbacken, NV om, Srm</t>
+          <t>Holmtorp, SO om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595658</v>
+        <v>595681</v>
       </c>
       <c r="R4" t="n">
-        <v>6549756</v>
+        <v>6549823</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,17 +955,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande på torra alar utmed stranden. Spillkråka är regelbundet förekommande inom området.</t>
+          <t>På grov granlåga i blockrik sluttning i gränsen mot granbestånd där de flesta granarna dödats av granbarkborrar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,6 +990,662 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116148432</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holmtorp, SO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595773</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6549805</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga 5m söder om en ek. Stort bestånd av granbarkborredödade granar väster om fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128681376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fredsbacken, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595809</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6549806</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På två granlågor som fallit över ett stort block.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129499211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmtorp, SO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595705</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6549846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe på nyligen avverkat hygge där granbarkborredödade granar avverkats och levande tallar, lövträd och enstaka granar sparats.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128990470</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fredsbacken, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595736</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6549780</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128681511</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fredsbacken, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595746</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6549774</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid roten av gammal tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131582075</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fredsbacken, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595658</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6549756</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökande på torra alar utmed stranden. Spillkråka är regelbundet förekommande inom området.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32901-2025 artfynd.xlsx
+++ b/artfynd/A 32901-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79281229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870887</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116148246</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116148432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129499211</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990470</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128681511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,8 +1691,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131582075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>